--- a/feedback_surveys/023_cylinder_feedback_form--feedback_surveys.xlsx
+++ b/feedback_surveys/023_cylinder_feedback_form--feedback_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1110,8 +1110,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very dissatisfied'}</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Very satisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'0-25'}</t>
+          <t>0-25</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '0-25'}</t>
+          <t>0-25</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'26-50'}</t>
+          <t>26-50</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '26-50'}</t>
+          <t>26-50</t>
         </is>
       </c>
     </row>
@@ -1377,12 +1377,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'51-75'}</t>
+          <t>51-75</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '51-75'}</t>
+          <t>51-75</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'76-100'}</t>
+          <t>76-100</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': '76-100'}</t>
+          <t>76-100</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1428,12 +1428,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1445,12 +1445,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'archived'}</t>
+          <t>archived</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Archived'}</t>
+          <t>Archived</t>
         </is>
       </c>
     </row>
